--- a/devis-api/template/devis_template.xlsx
+++ b/devis-api/template/devis_template.xlsx
@@ -1609,7 +1609,7 @@
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+      <alignment horizontal="right" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -1648,7 +1648,7 @@
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
